--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2323"/>
+  <dimension ref="A1:D2345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="7.69140625" bestFit="1" customWidth="1" style="9" min="1" max="1"/>
@@ -1361,7 +1361,7 @@
         <v>110.3</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>103.05</v>
+        <v>102.75</v>
       </c>
     </row>
     <row r="48">
@@ -2257,7 +2257,7 @@
         <v>124</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>100.05</v>
+        <v>99</v>
       </c>
     </row>
     <row r="104">
@@ -4737,7 +4737,7 @@
         <v>175</v>
       </c>
       <c r="D258" s="3" t="n">
-        <v>111</v>
+        <v>104.15</v>
       </c>
     </row>
     <row r="259">
@@ -5009,7 +5009,7 @@
         <v>135.7</v>
       </c>
       <c r="D275" s="3" t="n">
-        <v>109</v>
+        <v>108.95</v>
       </c>
     </row>
     <row r="276">
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="C286" s="3" t="n">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="D286" s="3" t="n">
         <v>102.2</v>
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="C392" s="3" t="n">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="D392" s="3" t="n">
         <v>110.2</v>
@@ -6894,7 +6894,7 @@
         </is>
       </c>
       <c r="C393" s="3" t="n">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="D393" s="3" t="n">
         <v>133.1</v>
@@ -11406,7 +11406,7 @@
         </is>
       </c>
       <c r="C675" s="3" t="n">
-        <v>666</v>
+        <v>740</v>
       </c>
       <c r="D675" s="3" t="n">
         <v>111.1</v>
@@ -11726,7 +11726,7 @@
         </is>
       </c>
       <c r="C695" s="3" t="n">
-        <v>108.8</v>
+        <v>109</v>
       </c>
       <c r="D695" s="3" t="n">
         <v>99.5</v>
@@ -16030,7 +16030,7 @@
         </is>
       </c>
       <c r="C964" s="3" t="n">
-        <v>145.5</v>
+        <v>146</v>
       </c>
       <c r="D964" s="3" t="n">
         <v>108.5</v>
@@ -16622,7 +16622,7 @@
         </is>
       </c>
       <c r="C1001" s="3" t="n">
-        <v>189</v>
+        <v>282</v>
       </c>
       <c r="D1001" s="3" t="n">
         <v>97</v>
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="C1008" s="3" t="n">
-        <v>118.95</v>
+        <v>120.95</v>
       </c>
       <c r="D1008" s="3" t="n">
         <v>99.84999999999999</v>
@@ -17745,7 +17745,7 @@
         <v>145.5</v>
       </c>
       <c r="D1071" s="3" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1072">
@@ -18369,7 +18369,7 @@
         <v>136.75</v>
       </c>
       <c r="D1110" s="3" t="n">
-        <v>94.5</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="1111">
@@ -18497,7 +18497,7 @@
         <v>130.5</v>
       </c>
       <c r="D1118" s="3" t="n">
-        <v>105.7</v>
+        <v>105.4</v>
       </c>
     </row>
     <row r="1119">
@@ -19550,7 +19550,7 @@
         </is>
       </c>
       <c r="C1184" s="3" t="n">
-        <v>108.75</v>
+        <v>112</v>
       </c>
       <c r="D1184" s="3" t="n">
         <v>92.84999999999999</v>
@@ -20177,7 +20177,7 @@
         <v>121</v>
       </c>
       <c r="D1223" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>99.65000000000001</v>
       </c>
     </row>
     <row r="1224">
@@ -22353,7 +22353,7 @@
         <v>123</v>
       </c>
       <c r="D1359" s="3" t="n">
-        <v>94.7</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1360">
@@ -22785,7 +22785,7 @@
         <v>135.3</v>
       </c>
       <c r="D1386" s="3" t="n">
-        <v>103</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="1387">
@@ -27678,7 +27678,7 @@
         </is>
       </c>
       <c r="C1692" s="3" t="n">
-        <v>130.15</v>
+        <v>132.7</v>
       </c>
       <c r="D1692" s="3" t="n">
         <v>105.55</v>
@@ -28241,7 +28241,7 @@
         <v>118.45</v>
       </c>
       <c r="D1727" s="3" t="n">
-        <v>101.5</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1728">
@@ -30942,7 +30942,7 @@
         </is>
       </c>
       <c r="C1896" s="3" t="n">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="D1896" s="3" t="n">
         <v>87.09999999999999</v>
@@ -30990,7 +30990,7 @@
         </is>
       </c>
       <c r="C1899" s="3" t="n">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="D1899" s="3" t="n">
         <v>115.4</v>
@@ -31265,7 +31265,7 @@
         <v>124</v>
       </c>
       <c r="D1916" s="3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="1917">
@@ -31825,7 +31825,7 @@
         <v>172</v>
       </c>
       <c r="D1951" s="3" t="n">
-        <v>100.05</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="1952">
@@ -31998,7 +31998,7 @@
         </is>
       </c>
       <c r="C1962" s="3" t="n">
-        <v>130.5</v>
+        <v>151</v>
       </c>
       <c r="D1962" s="3" t="n">
         <v>88.5</v>
@@ -32017,7 +32017,7 @@
         <v>115</v>
       </c>
       <c r="D1963" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="1964">
@@ -32049,7 +32049,7 @@
         <v>107.45</v>
       </c>
       <c r="D1965" s="3" t="n">
-        <v>94</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="1966">
@@ -32142,7 +32142,7 @@
         </is>
       </c>
       <c r="C1971" s="3" t="n">
-        <v>143.5</v>
+        <v>145</v>
       </c>
       <c r="D1971" s="3" t="n">
         <v>94.5</v>
@@ -32398,7 +32398,7 @@
         </is>
       </c>
       <c r="C1987" s="3" t="n">
-        <v>107.5</v>
+        <v>108</v>
       </c>
       <c r="D1987" s="3" t="n">
         <v>100.5</v>
@@ -34209,7 +34209,7 @@
         <v>136</v>
       </c>
       <c r="D2100" s="3" t="n">
-        <v>103</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="2101">
@@ -34926,7 +34926,7 @@
         </is>
       </c>
       <c r="C2145" s="3" t="n">
-        <v>103.2</v>
+        <v>103.25</v>
       </c>
       <c r="D2145" s="3" t="n">
         <v>99.3</v>
@@ -36990,7 +36990,7 @@
         </is>
       </c>
       <c r="C2274" s="6" t="n">
-        <v>141.5</v>
+        <v>145.5</v>
       </c>
       <c r="D2274" s="6" t="n">
         <v>92</v>
@@ -37105,7 +37105,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="D2281" s="0" t="n">
-        <v>89.5</v>
+        <v>86.05</v>
       </c>
     </row>
     <row r="2282">
@@ -37121,7 +37121,7 @@
         <v>98.8</v>
       </c>
       <c r="D2282" s="0" t="n">
-        <v>90.65000000000001</v>
+        <v>88.05</v>
       </c>
     </row>
     <row r="2283">
@@ -37137,7 +37137,7 @@
         <v>124</v>
       </c>
       <c r="D2283" s="0" t="n">
-        <v>110.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2284">
@@ -37153,7 +37153,7 @@
         <v>116.6</v>
       </c>
       <c r="D2284" s="0" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2285">
@@ -37249,7 +37249,7 @@
         <v>154</v>
       </c>
       <c r="D2290" s="0" t="n">
-        <v>115.25</v>
+        <v>115.2</v>
       </c>
     </row>
     <row r="2291">
@@ -37278,7 +37278,7 @@
         </is>
       </c>
       <c r="C2292" s="0" t="n">
-        <v>114</v>
+        <v>117.5</v>
       </c>
       <c r="D2292" s="0" t="n">
         <v>104.5</v>
@@ -37358,7 +37358,7 @@
         </is>
       </c>
       <c r="C2297" s="0" t="n">
-        <v>121.1</v>
+        <v>125.35</v>
       </c>
       <c r="D2297" s="0" t="n">
         <v>107</v>
@@ -37441,7 +37441,7 @@
         <v>132</v>
       </c>
       <c r="D2302" s="0" t="n">
-        <v>113.85</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2303">
@@ -37502,282 +37502,634 @@
         </is>
       </c>
       <c r="C2306" s="0" t="n">
-        <v>115.85</v>
+        <v>120.8</v>
       </c>
       <c r="D2306" s="0" t="n">
         <v>105</v>
       </c>
     </row>
     <row r="2307">
-      <c r="A2307" t="n">
+      <c r="A2307" s="0" t="n">
         <v>16231</v>
       </c>
-      <c r="B2307" t="inlineStr">
+      <c r="B2307" s="0" t="inlineStr">
         <is>
           <t>大東電一</t>
         </is>
       </c>
-      <c r="C2307" t="n">
+      <c r="C2307" s="0" t="n">
         <v>112</v>
       </c>
-      <c r="D2307" t="n">
-        <v>105.5</v>
+      <c r="D2307" s="0" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="2308">
-      <c r="A2308" t="n">
+      <c r="A2308" s="0" t="n">
         <v>24867</v>
       </c>
-      <c r="B2308" t="inlineStr">
+      <c r="B2308" s="0" t="inlineStr">
         <is>
           <t>一詮七</t>
         </is>
       </c>
-      <c r="C2308" t="n">
+      <c r="C2308" s="0" t="n">
         <v>132</v>
       </c>
-      <c r="D2308" t="n">
+      <c r="D2308" s="0" t="n">
         <v>110</v>
       </c>
     </row>
     <row r="2309">
-      <c r="A2309" t="n">
+      <c r="A2309" s="0" t="n">
         <v>30285</v>
       </c>
-      <c r="B2309" t="inlineStr">
+      <c r="B2309" s="0" t="inlineStr">
         <is>
           <t>增你強五</t>
         </is>
       </c>
-      <c r="C2309" t="n">
+      <c r="C2309" s="0" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="D2309" s="0" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" s="0" t="n">
+        <v>35833</v>
+      </c>
+      <c r="B2310" s="0" t="inlineStr">
+        <is>
+          <t>辛耘三</t>
+        </is>
+      </c>
+      <c r="C2310" s="0" t="n">
+        <v>134.95</v>
+      </c>
+      <c r="D2310" s="0" t="n">
+        <v>113.1</v>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" s="0" t="n">
+        <v>36054</v>
+      </c>
+      <c r="B2311" s="0" t="inlineStr">
+        <is>
+          <t>宏致四</t>
+        </is>
+      </c>
+      <c r="C2311" s="0" t="n">
+        <v>162</v>
+      </c>
+      <c r="D2311" s="0" t="n">
+        <v>110.55</v>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" s="0" t="n">
+        <v>52892</v>
+      </c>
+      <c r="B2312" s="0" t="inlineStr">
+        <is>
+          <t>宜鼎二</t>
+        </is>
+      </c>
+      <c r="C2312" s="0" t="n">
+        <v>124</v>
+      </c>
+      <c r="D2312" s="0" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" s="0" t="n">
+        <v>52912</v>
+      </c>
+      <c r="B2313" s="0" t="inlineStr">
+        <is>
+          <t>邑昇二</t>
+        </is>
+      </c>
+      <c r="C2313" s="0" t="n">
+        <v>132</v>
+      </c>
+      <c r="D2313" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" s="0" t="n">
+        <v>61343</v>
+      </c>
+      <c r="B2314" s="0" t="inlineStr">
+        <is>
+          <t>萬旭三</t>
+        </is>
+      </c>
+      <c r="C2314" s="0" t="n">
+        <v>132</v>
+      </c>
+      <c r="D2314" s="0" t="n">
+        <v>118.8</v>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" s="0" t="n">
+        <v>61876</v>
+      </c>
+      <c r="B2315" s="0" t="inlineStr">
+        <is>
+          <t>萬潤六</t>
+        </is>
+      </c>
+      <c r="C2315" s="0" t="n">
+        <v>149.2</v>
+      </c>
+      <c r="D2315" s="0" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="A2316" s="0" t="n">
+        <v>65843</v>
+      </c>
+      <c r="B2316" s="0" t="inlineStr">
+        <is>
+          <t>南俊國際三</t>
+        </is>
+      </c>
+      <c r="C2316" s="0" t="n">
+        <v>148</v>
+      </c>
+      <c r="D2316" s="0" t="n">
         <v>110</v>
       </c>
-      <c r="D2309" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2310">
-      <c r="A2310" t="n">
-        <v>35833</v>
-      </c>
-      <c r="B2310" t="inlineStr">
-        <is>
-          <t>辛耘三</t>
-        </is>
-      </c>
-      <c r="C2310" t="n">
-        <v>121</v>
-      </c>
-      <c r="D2310" t="n">
-        <v>113.1</v>
-      </c>
-    </row>
-    <row r="2311">
-      <c r="A2311" t="n">
-        <v>36054</v>
-      </c>
-      <c r="B2311" t="inlineStr">
-        <is>
-          <t>宏致四</t>
-        </is>
-      </c>
-      <c r="C2311" t="n">
-        <v>133.75</v>
-      </c>
-      <c r="D2311" t="n">
+    </row>
+    <row r="2317">
+      <c r="A2317" s="0" t="n">
+        <v>66931</v>
+      </c>
+      <c r="B2317" s="0" t="inlineStr">
+        <is>
+          <t>廣閎科一</t>
+        </is>
+      </c>
+      <c r="C2317" s="0" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="D2317" s="0" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="A2318" s="0" t="n">
+        <v>68692</v>
+      </c>
+      <c r="B2318" s="0" t="inlineStr">
+        <is>
+          <t>雲豹能源二</t>
+        </is>
+      </c>
+      <c r="C2318" s="0" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="D2318" s="0" t="n">
+        <v>106.1</v>
+      </c>
+    </row>
+    <row r="2319">
+      <c r="A2319" s="0" t="n">
+        <v>69031</v>
+      </c>
+      <c r="B2319" s="0" t="inlineStr">
+        <is>
+          <t>巨漢一</t>
+        </is>
+      </c>
+      <c r="C2319" s="0" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="D2319" s="0" t="n">
+        <v>106.5</v>
+      </c>
+    </row>
+    <row r="2320">
+      <c r="A2320" s="0" t="n">
+        <v>80541</v>
+      </c>
+      <c r="B2320" s="0" t="inlineStr">
+        <is>
+          <t>安國一</t>
+        </is>
+      </c>
+      <c r="C2320" s="0" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="D2320" s="0" t="n">
+        <v>115.5</v>
+      </c>
+    </row>
+    <row r="2321">
+      <c r="A2321" s="0" t="n">
+        <v>80962</v>
+      </c>
+      <c r="B2321" s="0" t="inlineStr">
+        <is>
+          <t>擎亞二</t>
+        </is>
+      </c>
+      <c r="C2321" s="0" t="n">
+        <v>126</v>
+      </c>
+      <c r="D2321" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="A2322" s="0" t="n">
+        <v>80963</v>
+      </c>
+      <c r="B2322" s="0" t="inlineStr">
+        <is>
+          <t>擎亞三</t>
+        </is>
+      </c>
+      <c r="C2322" s="0" t="n">
+        <v>118</v>
+      </c>
+      <c r="D2322" s="0" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="A2323" s="0" t="n">
+        <v>84423</v>
+      </c>
+      <c r="B2323" s="0" t="inlineStr">
+        <is>
+          <t>威宏三KY</t>
+        </is>
+      </c>
+      <c r="C2323" s="0" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="D2323" s="0" t="n">
+        <v>111.65</v>
+      </c>
+    </row>
+    <row r="2324">
+      <c r="A2324" t="n">
+        <v>23031</v>
+      </c>
+      <c r="B2324" t="inlineStr">
+        <is>
+          <t>聯電一</t>
+        </is>
+      </c>
+      <c r="C2324" t="n">
+        <v>124.65</v>
+      </c>
+      <c r="D2324" t="n">
+        <v>111.1</v>
+      </c>
+    </row>
+    <row r="2325">
+      <c r="A2325" t="n">
+        <v>30166</v>
+      </c>
+      <c r="B2325" t="inlineStr">
+        <is>
+          <t>嘉晶六</t>
+        </is>
+      </c>
+      <c r="C2325" t="n">
+        <v>123.05</v>
+      </c>
+      <c r="D2325" t="n">
+        <v>111.1</v>
+      </c>
+    </row>
+    <row r="2326">
+      <c r="A2326" t="n">
+        <v>30811</v>
+      </c>
+      <c r="B2326" t="inlineStr">
+        <is>
+          <t>聯亞一</t>
+        </is>
+      </c>
+      <c r="C2326" t="n">
+        <v>234</v>
+      </c>
+      <c r="D2326" t="n">
+        <v>149.85</v>
+      </c>
+    </row>
+    <row r="2327">
+      <c r="A2327" t="n">
+        <v>30812</v>
+      </c>
+      <c r="B2327" t="inlineStr">
+        <is>
+          <t>聯亞二</t>
+        </is>
+      </c>
+      <c r="C2327" t="n">
+        <v>194</v>
+      </c>
+      <c r="D2327" t="n">
+        <v>114.4</v>
+      </c>
+    </row>
+    <row r="2328">
+      <c r="A2328" t="n">
+        <v>31414</v>
+      </c>
+      <c r="B2328" t="inlineStr">
+        <is>
+          <t>晶宏四</t>
+        </is>
+      </c>
+      <c r="C2328" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="D2328" t="n">
+        <v>115.6</v>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" t="n">
+        <v>31494</v>
+      </c>
+      <c r="B2329" t="inlineStr">
+        <is>
+          <t>正達四</t>
+        </is>
+      </c>
+      <c r="C2329" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="D2329" t="n">
+        <v>116.5</v>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" t="n">
+        <v>32191</v>
+      </c>
+      <c r="B2330" t="inlineStr">
+        <is>
+          <t>倚強科一</t>
+        </is>
+      </c>
+      <c r="C2330" t="n">
+        <v>135.8</v>
+      </c>
+      <c r="D2330" t="n">
+        <v>109.5</v>
+      </c>
+    </row>
+    <row r="2331">
+      <c r="A2331" t="n">
+        <v>35122</v>
+      </c>
+      <c r="B2331" t="inlineStr">
+        <is>
+          <t>皇龍二</t>
+        </is>
+      </c>
+      <c r="C2331" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="D2331" t="n">
+        <v>101.8</v>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="A2332" t="n">
+        <v>47642</v>
+      </c>
+      <c r="B2332" t="inlineStr">
+        <is>
+          <t>雙鍵二</t>
+        </is>
+      </c>
+      <c r="C2332" t="n">
+        <v>132.2</v>
+      </c>
+      <c r="D2332" t="n">
+        <v>119.8</v>
+      </c>
+    </row>
+    <row r="2333">
+      <c r="A2333" t="n">
+        <v>49675</v>
+      </c>
+      <c r="B2333" t="inlineStr">
+        <is>
+          <t>十銓五</t>
+        </is>
+      </c>
+      <c r="C2333" t="n">
+        <v>136.95</v>
+      </c>
+      <c r="D2333" t="n">
+        <v>122.4</v>
+      </c>
+    </row>
+    <row r="2334">
+      <c r="A2334" t="n">
+        <v>49731</v>
+      </c>
+      <c r="B2334" t="inlineStr">
+        <is>
+          <t>廣穎電通一</t>
+        </is>
+      </c>
+      <c r="C2334" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="D2334" t="n">
+        <v>105.05</v>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" t="n">
+        <v>55362</v>
+      </c>
+      <c r="B2335" t="inlineStr">
+        <is>
+          <t>聖暉二</t>
+        </is>
+      </c>
+      <c r="C2335" t="n">
+        <v>131</v>
+      </c>
+      <c r="D2335" t="n">
+        <v>112.2</v>
+      </c>
+    </row>
+    <row r="2336">
+      <c r="A2336" t="n">
+        <v>55363</v>
+      </c>
+      <c r="B2336" t="inlineStr">
+        <is>
+          <t>聖暉三</t>
+        </is>
+      </c>
+      <c r="C2336" t="n">
+        <v>125.2</v>
+      </c>
+      <c r="D2336" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="A2337" t="n">
+        <v>65702</v>
+      </c>
+      <c r="B2337" t="inlineStr">
+        <is>
+          <t>維田二</t>
+        </is>
+      </c>
+      <c r="C2337" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="D2337" t="n">
+        <v>104.6</v>
+      </c>
+    </row>
+    <row r="2338">
+      <c r="A2338" t="n">
+        <v>66831</v>
+      </c>
+      <c r="B2338" t="inlineStr">
+        <is>
+          <t>雍智一</t>
+        </is>
+      </c>
+      <c r="C2338" t="n">
+        <v>146.5</v>
+      </c>
+      <c r="D2338" t="n">
+        <v>128.15</v>
+      </c>
+    </row>
+    <row r="2339">
+      <c r="A2339" t="n">
+        <v>69032</v>
+      </c>
+      <c r="B2339" t="inlineStr">
+        <is>
+          <t>巨漢二</t>
+        </is>
+      </c>
+      <c r="C2339" t="n">
+        <v>120</v>
+      </c>
+      <c r="D2339" t="n">
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="2340">
+      <c r="A2340" t="n">
+        <v>76311</v>
+      </c>
+      <c r="B2340" t="inlineStr">
+        <is>
+          <t>聚賢研發一創</t>
+        </is>
+      </c>
+      <c r="C2340" t="n">
         <v>110.55</v>
       </c>
-    </row>
-    <row r="2312">
-      <c r="A2312" t="n">
-        <v>52892</v>
-      </c>
-      <c r="B2312" t="inlineStr">
-        <is>
-          <t>宜鼎二</t>
-        </is>
-      </c>
-      <c r="C2312" t="n">
-        <v>122.5</v>
-      </c>
-      <c r="D2312" t="n">
+      <c r="D2340" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2341">
+      <c r="A2341" t="n">
+        <v>81552</v>
+      </c>
+      <c r="B2341" t="inlineStr">
+        <is>
+          <t>博智二</t>
+        </is>
+      </c>
+      <c r="C2341" t="n">
+        <v>127</v>
+      </c>
+      <c r="D2341" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="A2342" t="n">
+        <v>81553</v>
+      </c>
+      <c r="B2342" t="inlineStr">
+        <is>
+          <t>博智三</t>
+        </is>
+      </c>
+      <c r="C2342" t="n">
+        <v>132</v>
+      </c>
+      <c r="D2342" t="n">
+        <v>116.25</v>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" t="n">
+        <v>84381</v>
+      </c>
+      <c r="B2343" t="inlineStr">
+        <is>
+          <t>昶昕一</t>
+        </is>
+      </c>
+      <c r="C2343" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="D2343" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" t="n">
+        <v>89365</v>
+      </c>
+      <c r="B2344" t="inlineStr">
+        <is>
+          <t>國統五</t>
+        </is>
+      </c>
+      <c r="C2344" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="D2344" t="n">
         <v>109</v>
       </c>
     </row>
-    <row r="2313">
-      <c r="A2313" t="n">
-        <v>52912</v>
-      </c>
-      <c r="B2313" t="inlineStr">
-        <is>
-          <t>邑昇二</t>
-        </is>
-      </c>
-      <c r="C2313" t="n">
-        <v>111</v>
-      </c>
-      <c r="D2313" t="n">
-        <v>108.55</v>
-      </c>
-    </row>
-    <row r="2314">
-      <c r="A2314" t="n">
-        <v>61343</v>
-      </c>
-      <c r="B2314" t="inlineStr">
-        <is>
-          <t>萬旭三</t>
-        </is>
-      </c>
-      <c r="C2314" t="n">
-        <v>122.5</v>
-      </c>
-      <c r="D2314" t="n">
-        <v>118.8</v>
-      </c>
-    </row>
-    <row r="2315">
-      <c r="A2315" t="n">
-        <v>61876</v>
-      </c>
-      <c r="B2315" t="inlineStr">
-        <is>
-          <t>萬潤六</t>
-        </is>
-      </c>
-      <c r="C2315" t="n">
-        <v>141</v>
-      </c>
-      <c r="D2315" t="n">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="2316">
-      <c r="A2316" t="n">
-        <v>65843</v>
-      </c>
-      <c r="B2316" t="inlineStr">
-        <is>
-          <t>南俊國際三</t>
-        </is>
-      </c>
-      <c r="C2316" t="n">
-        <v>148</v>
-      </c>
-      <c r="D2316" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2317">
-      <c r="A2317" t="n">
-        <v>66931</v>
-      </c>
-      <c r="B2317" t="inlineStr">
-        <is>
-          <t>廣閎科一</t>
-        </is>
-      </c>
-      <c r="C2317" t="n">
-        <v>114.5</v>
-      </c>
-      <c r="D2317" t="n">
+    <row r="2345">
+      <c r="A2345" t="n">
+        <v>89366</v>
+      </c>
+      <c r="B2345" t="inlineStr">
+        <is>
+          <t>國統六</t>
+        </is>
+      </c>
+      <c r="C2345" t="n">
         <v>104</v>
       </c>
-    </row>
-    <row r="2318">
-      <c r="A2318" t="n">
-        <v>68692</v>
-      </c>
-      <c r="B2318" t="inlineStr">
-        <is>
-          <t>雲豹能源二</t>
-        </is>
-      </c>
-      <c r="C2318" t="n">
-        <v>111.95</v>
-      </c>
-      <c r="D2318" t="n">
-        <v>106.1</v>
-      </c>
-    </row>
-    <row r="2319">
-      <c r="A2319" t="n">
-        <v>69031</v>
-      </c>
-      <c r="B2319" t="inlineStr">
-        <is>
-          <t>巨漢一</t>
-        </is>
-      </c>
-      <c r="C2319" t="n">
-        <v>121.5</v>
-      </c>
-      <c r="D2319" t="n">
-        <v>106.5</v>
-      </c>
-    </row>
-    <row r="2320">
-      <c r="A2320" t="n">
-        <v>80541</v>
-      </c>
-      <c r="B2320" t="inlineStr">
-        <is>
-          <t>安國一</t>
-        </is>
-      </c>
-      <c r="C2320" t="n">
-        <v>121.5</v>
-      </c>
-      <c r="D2320" t="n">
-        <v>115.5</v>
-      </c>
-    </row>
-    <row r="2321">
-      <c r="A2321" t="n">
-        <v>80962</v>
-      </c>
-      <c r="B2321" t="inlineStr">
-        <is>
-          <t>擎亞二</t>
-        </is>
-      </c>
-      <c r="C2321" t="n">
-        <v>126</v>
-      </c>
-      <c r="D2321" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2322">
-      <c r="A2322" t="n">
-        <v>80963</v>
-      </c>
-      <c r="B2322" t="inlineStr">
-        <is>
-          <t>擎亞三</t>
-        </is>
-      </c>
-      <c r="C2322" t="n">
-        <v>118</v>
-      </c>
-      <c r="D2322" t="n">
-        <v>105.05</v>
-      </c>
-    </row>
-    <row r="2323">
-      <c r="A2323" t="n">
-        <v>84423</v>
-      </c>
-      <c r="B2323" t="inlineStr">
-        <is>
-          <t>威宏三KY</t>
-        </is>
-      </c>
-      <c r="C2323" t="n">
-        <v>114.1</v>
-      </c>
-      <c r="D2323" t="n">
-        <v>111.85</v>
+      <c r="D2345" t="n">
+        <v>101.5</v>
       </c>
     </row>
   </sheetData>
